--- a/Industrials.xlsx
+++ b/Industrials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4FDC392-97E0-4E6C-AB4C-9516F3BC88E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D60C32-9CB8-4579-9DAB-51040EE12576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="2" xr2:uid="{BC09624D-2BC9-4D8E-825C-85DD97F4255E}"/>
+    <workbookView xWindow="225" yWindow="3900" windowWidth="38175" windowHeight="15240" activeTab="4" xr2:uid="{BC09624D-2BC9-4D8E-825C-85DD97F4255E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3388" uniqueCount="2216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3391" uniqueCount="2218">
   <si>
     <t>Industrials Universe</t>
   </si>
@@ -6728,6 +6728,12 @@
   </si>
   <si>
     <t>VOYG</t>
+  </si>
+  <si>
+    <t>Smith &amp; Wesson</t>
+  </si>
+  <si>
+    <t>SWBI</t>
   </si>
 </sst>
 </file>
@@ -6934,22 +6940,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2">
-            <v>254.5</v>
+            <v>312.19</v>
           </cell>
         </row>
         <row r="4">
           <cell r="K4">
-            <v>819733.35569950007</v>
+            <v>1006952.8886569099</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>36996</v>
+            <v>36782</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>7529</v>
+            <v>7220</v>
           </cell>
         </row>
       </sheetData>
@@ -7323,22 +7329,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>83.19</v>
+            <v>90.18</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>173964.27407262</v>
+            <v>188063.05620167998</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>7279</v>
+            <v>6977</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>8350</v>
+            <v>8347</v>
           </cell>
         </row>
       </sheetData>
@@ -8762,19 +8768,19 @@
       </c>
       <c r="E4" s="7">
         <f>+[1]Main!$K$2</f>
-        <v>254.5</v>
+        <v>312.19</v>
       </c>
       <c r="F4" s="8">
         <f>+[1]Main!$K$4</f>
-        <v>819733.35569950007</v>
+        <v>1006952.8886569099</v>
       </c>
       <c r="G4" s="8">
         <f>+[1]Main!$K$6-[1]Main!$K$5</f>
-        <v>-29467</v>
+        <v>-29562</v>
       </c>
       <c r="H4" s="8">
         <f>+F4+G4</f>
-        <v>790266.35569950007</v>
+        <v>977390.88865690993</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>236</v>
@@ -10143,19 +10149,19 @@
       </c>
       <c r="E5" s="20">
         <f>+[1]Main!$K$2</f>
-        <v>254.5</v>
+        <v>312.19</v>
       </c>
       <c r="F5" s="8">
         <f>+[1]Main!$K$4</f>
-        <v>819733.35569950007</v>
+        <v>1006952.8886569099</v>
       </c>
       <c r="G5" s="8">
         <f>+[1]Main!$K$6-[1]Main!$K$5</f>
-        <v>-29467</v>
+        <v>-29562</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
-        <v>790266.35569950007</v>
+        <v>977390.88865690993</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>236</v>
@@ -23929,19 +23935,19 @@
       </c>
       <c r="E4">
         <f>+[19]Main!$H$2</f>
-        <v>83.19</v>
+        <v>90.18</v>
       </c>
       <c r="F4" s="8">
         <f>+[19]Main!$H$4</f>
-        <v>173964.27407262</v>
+        <v>188063.05620167998</v>
       </c>
       <c r="G4" s="8">
         <f>+[19]Main!$H$6-[19]Main!$H$5</f>
-        <v>1071</v>
+        <v>1370</v>
       </c>
       <c r="H4" s="8">
         <f>+F4+G4</f>
-        <v>175035.27407262</v>
+        <v>189433.05620167998</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>2200</v>
@@ -30126,6 +30132,15 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
+      <c r="B41" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2217</v>
+      </c>
+      <c r="D41" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B43" s="16" t="s">
